--- a/DATA/demand/Forecast_demand_data.xlsx
+++ b/DATA/demand/Forecast_demand_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/demand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="8_{90B69A98-A806-4331-9DFD-B75E3626E765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D5AA19-BC84-4A22-B20C-9D5D29690129}"/>
+  <xr:revisionPtr revIDLastSave="341" documentId="8_{90B69A98-A806-4331-9DFD-B75E3626E765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8C98D3C-9D1D-48E9-95EC-5107B5215C8A}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{ADCB78BC-AF59-4031-B361-4F9BE8F7CC28}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{ADCB78BC-AF59-4031-B361-4F9BE8F7CC28}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="65">
   <si>
     <t>Vaccine</t>
   </si>
@@ -236,6 +236,9 @@
   <si>
     <t>OPV</t>
   </si>
+  <si>
+    <t>Total</t>
+  </si>
 </sst>
 </file>
 
@@ -285,7 +288,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -308,11 +311,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -332,6 +346,9 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -347,6 +364,2259 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Measles</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$2:$Y$2</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>184600677</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>169922012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>341329845</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>307378677</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>380696579</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>586313630</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>475240096</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>291360748</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>420097004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>358616887</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>394831633</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mumps</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$3:$Y$3</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>22105642</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19837777</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26434485</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20737739</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20303126</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23934205</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21792972</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18694960</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26052156</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26626399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25785425</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rubella</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$4:$Y$4</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>37190191</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43940031</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>128302869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110243636</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>186643246</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>434104155</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>354218405</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>212986007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>357331305</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>254011421</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>304621416</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Diphtheria</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$5:$Y$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>358960052</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>354880969</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>362257229</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>402799889</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>429658592</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>474101067</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>595266022</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>606971011</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>570550152</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>619539916</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>626455401</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tetanus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$6:$Y$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>523242808</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>528432014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>540142924</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>552631403</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>615744020</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>638869328</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>637765782</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>617489918</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>577730183</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>626350955</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>633278479</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pertussis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$7:$Y$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>328701755</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>323938145</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>325441283</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>326230496</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>333387964</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>341894642</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>348615177</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>333074171</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>320662742</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>347414024</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>352464578</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hepatitis_B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$8:$Y$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>307013342</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>304655315</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>306586598</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>310915297</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>318821586</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>332337842</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>340059522</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>329290310</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>312284565</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>343008157</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>351717780</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hib</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$9:$Y$9</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>154141277</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>175806595</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>234434326</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>261706481</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>267997879</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>277236714</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>283780799</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>272465350</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>259536228</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>282777104</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>287252889</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Polio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$10:$Y$10</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>354511503.71144724</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>355186102.64560306</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>371591674.63909698</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>459148209.50212324</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>510749541.40994167</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>520616139.799227</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>545892364.24520755</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>525681082.76769733</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>522182008.89205366</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>582182282.26193905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>608631764.96709085</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HPV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$11:$Y$11</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>181341</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>349925</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>514654</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1545657</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2487801</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6959717</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10275961</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12011982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18988210</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18779835</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>27459977</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rotavirus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$12:$Y$12</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>21235066</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35141119</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44497769</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55341924</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>66664537</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93092909</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>126525666</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>142261312</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>142479003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>166422083</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>173751395</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Demand!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PCV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Demand!$B$1:$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Demand!$B$13:$Y$13</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>41170015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>66222136</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>89756384</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>107603981</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>127327221</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>136528866</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>145562505</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>141811833</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>160800233</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>186996097</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>209165466</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-9C6F-405F-8514-1E7B127C9824}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1242098751"/>
+        <c:axId val="1242099711"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1242098751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1242099711"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1242099711"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1242098751"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>263524</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>117474</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>412749</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>177799</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98F17706-7EA4-DC06-2CA7-2B1E85E4AC19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -673,7 +2943,8 @@
   <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -1943,6 +4214,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10318,7 +12590,7 @@
         <v>301694795.28999996</v>
       </c>
       <c r="C40" s="6">
-        <f t="shared" ref="C40:Z40" si="0">D33+D32+D3+D2</f>
+        <f t="shared" ref="C40:Y40" si="0">D33+D32+D3+D2</f>
         <v>325020669.98644739</v>
       </c>
       <c r="D40" s="6">
@@ -10420,7 +12692,7 @@
         <v>20923950.020323381</v>
       </c>
       <c r="C41" s="6">
-        <f t="shared" ref="C41:Z41" si="1">D4+D5</f>
+        <f t="shared" ref="C41:Y41" si="1">D4+D5</f>
         <v>20532693.853786986</v>
       </c>
       <c r="D41" s="6">
@@ -10522,7 +12794,7 @@
         <v>311598814.06162727</v>
       </c>
       <c r="C42" s="6">
-        <f t="shared" ref="C42:Z42" si="2">D6+D7</f>
+        <f t="shared" ref="C42:Y42" si="2">D6+D7</f>
         <v>314913212.59057081</v>
       </c>
       <c r="D42" s="6">
@@ -10624,7 +12896,7 @@
         <v>5598384.2381578945</v>
       </c>
       <c r="C43" s="6">
-        <f t="shared" ref="C43:Z43" si="3">D8+D9</f>
+        <f t="shared" ref="C43:Y43" si="3">D8+D9</f>
         <v>11321282.009342104</v>
       </c>
       <c r="D43" s="6">
@@ -10726,7 +12998,7 @@
         <v>4569986.5263157897</v>
       </c>
       <c r="C44" s="6">
-        <f t="shared" ref="C44:Z44" si="4">D10+D11</f>
+        <f t="shared" ref="C44:Y44" si="4">D10+D11</f>
         <v>2613786.0340789473</v>
       </c>
       <c r="D44" s="6">
@@ -10828,7 +13100,7 @@
         <v>20888757.51754386</v>
       </c>
       <c r="C45" s="6">
-        <f t="shared" ref="C45:Z45" si="5">D12+D13</f>
+        <f t="shared" ref="C45:Y45" si="5">D12+D13</f>
         <v>23446088.279385965</v>
       </c>
       <c r="D45" s="6">
@@ -10930,7 +13202,7 @@
         <v>804259.78947368416</v>
       </c>
       <c r="C46" s="6">
-        <f t="shared" ref="C46:Y46" si="6">D14+D15</f>
+        <f t="shared" ref="C46:X46" si="6">D14+D15</f>
         <v>814409.56736842101</v>
       </c>
       <c r="D46" s="6">
@@ -11032,7 +13304,7 @@
         <v>0</v>
       </c>
       <c r="C47">
-        <f t="shared" ref="C47:Z47" si="7">D16+D17</f>
+        <f t="shared" ref="C47:Y47" si="7">D16+D17</f>
         <v>0</v>
       </c>
       <c r="D47">
@@ -11133,7 +13405,7 @@
         <v>0</v>
       </c>
       <c r="C48">
-        <f t="shared" ref="C48:Z48" si="8">D18+D19</f>
+        <f t="shared" ref="C48:Y48" si="8">D18+D19</f>
         <v>0</v>
       </c>
       <c r="D48">
@@ -11234,7 +13506,7 @@
         <v>78580259.047222212</v>
       </c>
       <c r="C49" s="6">
-        <f t="shared" ref="C49:Z49" si="9">D20+D21</f>
+        <f t="shared" ref="C49:Y49" si="9">D20+D21</f>
         <v>81681321.359730586</v>
       </c>
       <c r="D49" s="6">
@@ -11336,7 +13608,7 @@
         <v>14895546.665213035</v>
       </c>
       <c r="C50" s="6">
-        <f t="shared" ref="C50:Z50" si="10">D22+D23</f>
+        <f t="shared" ref="C50:Y50" si="10">D22+D23</f>
         <v>15916936.7598325</v>
       </c>
       <c r="D50" s="6">
@@ -11438,7 +13710,7 @@
         <v>16708549.179678362</v>
       </c>
       <c r="C51" s="6">
-        <f t="shared" ref="C51:Z51" si="11">D24+D25</f>
+        <f t="shared" ref="C51:Y51" si="11">D24+D25</f>
         <v>16708884.350394737</v>
       </c>
       <c r="D51" s="6">
@@ -11540,7 +13812,7 @@
         <v>0</v>
       </c>
       <c r="C52">
-        <f t="shared" ref="C52:Z52" si="12">D26+D27</f>
+        <f t="shared" ref="C52:Y52" si="12">D26+D27</f>
         <v>0</v>
       </c>
       <c r="D52">
@@ -11641,7 +13913,7 @@
         <v>0</v>
       </c>
       <c r="C53">
-        <f t="shared" ref="C53:Z53" si="13">D28+D29</f>
+        <f t="shared" ref="C53:Y53" si="13">D28+D29</f>
         <v>0</v>
       </c>
       <c r="D53">
@@ -11742,7 +14014,7 @@
         <v>50764265.476614729</v>
       </c>
       <c r="C54" s="6">
-        <f t="shared" ref="C54:Z54" si="14">D30+D31</f>
+        <f t="shared" ref="C54:Y54" si="14">D30+D31</f>
         <v>50774337.539247289</v>
       </c>
       <c r="D54" s="6">
@@ -11844,7 +14116,7 @@
         <v>78159428.70084165</v>
       </c>
       <c r="C55" s="6">
-        <f t="shared" ref="C55:Z55" si="15">D34+D35</f>
+        <f t="shared" ref="C55:Y55" si="15">D34+D35</f>
         <v>79754932.221154869</v>
       </c>
       <c r="D55" s="6">
@@ -12162,10 +14434,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493E7107-CCF2-4DA0-80AB-54EC2EAC2B5F}">
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="9.140625" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -13477,6 +15751,55 @@
         <v>209165465.89669368</v>
       </c>
     </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O18">
+        <f>O10+O9+O8+O7</f>
+        <v>297906042.12333</v>
+      </c>
+      <c r="P18">
+        <f t="shared" ref="P18:Y18" si="0">P10+P9+P8+P7</f>
+        <v>316379956.86790735</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="0"/>
+        <v>327328563.41181928</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="0"/>
+        <v>328014982.9608357</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="0"/>
+        <v>335588476.6396088</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="0"/>
+        <v>344112331.14668965</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="0"/>
+        <v>350792965.0256089</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="0"/>
+        <v>338136982.63314891</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="0"/>
+        <v>327067643.71307546</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="0"/>
+        <v>353856363.15045118</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="0"/>
+        <v>359006145.47024202</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
